--- a/templates/finance-calculators.xlsx
+++ b/templates/finance-calculators.xlsx
@@ -24,7 +24,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="$#,##0"/>
+    <numFmt numFmtId="165" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
+  </numFmts>
   <fonts count="5">
     <font>
       <name val="Calibri"/>
@@ -93,16 +98,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -466,7 +481,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -584,6 +599,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -591,7 +607,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -628,7 +644,7 @@
           <t>Price per unit</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="6" t="n">
         <v>4</v>
       </c>
     </row>
@@ -638,7 +654,7 @@
           <t>Variable cost per unit</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="6" t="n">
         <v>2.4</v>
       </c>
     </row>
@@ -658,7 +674,7 @@
           <t>Forecast units</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="7" t="n">
         <v>1200000</v>
       </c>
     </row>
@@ -675,7 +691,7 @@
           <t>Contribution per unit</t>
         </is>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="8">
         <f>B5-B6</f>
         <v/>
       </c>
@@ -686,7 +702,7 @@
           <t>Break-even units</t>
         </is>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="9">
         <f>B7/B11</f>
         <v/>
       </c>
@@ -697,7 +713,7 @@
           <t>Gap to break-even (units)</t>
         </is>
       </c>
-      <c r="B13" s="5">
+      <c r="B13" s="9">
         <f>B12-B8</f>
         <v/>
       </c>
@@ -709,6 +725,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -716,7 +733,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -754,7 +771,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>36000000</v>
+        <v>30000000</v>
       </c>
     </row>
     <row r="6">
@@ -800,7 +817,7 @@
           <t>Profit margin</t>
         </is>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="10">
         <f>B5/B6</f>
         <v/>
       </c>
@@ -811,7 +828,7 @@
           <t>Asset turnover</t>
         </is>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="11">
         <f>B6/B7</f>
         <v/>
       </c>
@@ -822,7 +839,7 @@
           <t>Equity multiplier</t>
         </is>
       </c>
-      <c r="B13" s="5">
+      <c r="B13" s="11">
         <f>B7/B8</f>
         <v/>
       </c>
@@ -833,13 +850,14 @@
           <t>ROE</t>
         </is>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="10">
         <f>B11*B12*B13</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -847,7 +865,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -884,7 +902,7 @@
           <t>Required return (0-1)</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="12" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -899,17 +917,17 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>Cash in</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>Present value</t>
         </is>
@@ -919,10 +937,10 @@
       <c r="A9" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="7" t="n">
+      <c r="B9" s="14" t="n">
         <v>12000000</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="15">
         <f>B9/(1+$B$5)^A9</f>
         <v/>
       </c>
@@ -931,10 +949,10 @@
       <c r="A10" t="n">
         <v>2</v>
       </c>
-      <c r="B10" s="7" t="n">
+      <c r="B10" s="14" t="n">
         <v>12000000</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="15">
         <f>B10/(1+$B$5)^A10</f>
         <v/>
       </c>
@@ -943,10 +961,10 @@
       <c r="A11" t="n">
         <v>3</v>
       </c>
-      <c r="B11" s="7" t="n">
+      <c r="B11" s="14" t="n">
         <v>12000000</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="15">
         <f>B11/(1+$B$5)^A11</f>
         <v/>
       </c>
@@ -955,10 +973,10 @@
       <c r="A12" t="n">
         <v>4</v>
       </c>
-      <c r="B12" s="7" t="n">
+      <c r="B12" s="14" t="n">
         <v>12000000</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="15">
         <f>B12/(1+$B$5)^A12</f>
         <v/>
       </c>
@@ -967,10 +985,10 @@
       <c r="A13" t="n">
         <v>5</v>
       </c>
-      <c r="B13" s="7" t="n">
+      <c r="B13" s="14" t="n">
         <v>12000000</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="15">
         <f>B13/(1+$B$5)^A13</f>
         <v/>
       </c>
@@ -979,10 +997,10 @@
       <c r="A14" t="n">
         <v>6</v>
       </c>
-      <c r="B14" s="7" t="n">
+      <c r="B14" s="14" t="n">
         <v>12000000</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="15">
         <f>B14/(1+$B$5)^A14</f>
         <v/>
       </c>
@@ -991,10 +1009,10 @@
       <c r="A15" t="n">
         <v>7</v>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="14" t="n">
         <v>12000000</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="15">
         <f>B15/(1+$B$5)^A15</f>
         <v/>
       </c>
@@ -1003,10 +1021,10 @@
       <c r="A16" t="n">
         <v>8</v>
       </c>
-      <c r="B16" s="7" t="n">
+      <c r="B16" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="15">
         <f>B16/(1+$B$5)^A16</f>
         <v/>
       </c>
@@ -1015,10 +1033,10 @@
       <c r="A17" t="n">
         <v>9</v>
       </c>
-      <c r="B17" s="7" t="n">
+      <c r="B17" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="15">
         <f>B17/(1+$B$5)^A17</f>
         <v/>
       </c>
@@ -1027,10 +1045,10 @@
       <c r="A18" t="n">
         <v>10</v>
       </c>
-      <c r="B18" s="7" t="n">
+      <c r="B18" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="15">
         <f>B18/(1+$B$5)^A18</f>
         <v/>
       </c>
@@ -1041,7 +1059,7 @@
           <t>Present value of cash flows</t>
         </is>
       </c>
-      <c r="B20" s="8">
+      <c r="B20" s="15">
         <f>SUM(C9:C18)</f>
         <v/>
       </c>
@@ -1052,7 +1070,7 @@
           <t>NPV</t>
         </is>
       </c>
-      <c r="B21" s="8">
+      <c r="B21" s="15">
         <f>B20-B6</f>
         <v/>
       </c>
@@ -1066,6 +1084,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1073,7 +1092,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1111,7 +1130,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>60000000</v>
+        <v>45000000</v>
       </c>
     </row>
     <row r="6">
@@ -1151,7 +1170,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>45000000</v>
+        <v>36000000</v>
       </c>
     </row>
     <row r="11">
@@ -1167,7 +1186,7 @@
           <t>Coverage ratio</t>
         </is>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="11">
         <f>B5/(B6+B7)</f>
         <v/>
       </c>
@@ -1183,7 +1202,7 @@
           <t>Coverage with higher rates</t>
         </is>
       </c>
-      <c r="B13" s="5">
+      <c r="B13" s="11">
         <f>B5/(B6+B8)</f>
         <v/>
       </c>
@@ -1194,13 +1213,14 @@
           <t>Coverage in a bad year with higher rates</t>
         </is>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="11">
         <f>B9/(B6+B8)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1208,7 +1228,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1246,7 +1266,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>38000000</v>
+        <v>44000000</v>
       </c>
     </row>
     <row r="6">
@@ -1256,7 +1276,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>10000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="7">
@@ -1266,7 +1286,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2000000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="8">
@@ -1275,7 +1295,7 @@
           <t>Entry multiple (× EBITDA)</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="16" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1305,7 +1325,7 @@
           <t>Exit multiple</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="16" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1376,7 +1396,7 @@
           <t>Money multiple</t>
         </is>
       </c>
-      <c r="B19" s="5">
+      <c r="B19" s="11">
         <f>B18/B9</f>
         <v/>
       </c>
@@ -1388,6 +1408,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1395,7 +1416,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1432,7 +1453,7 @@
           <t>Next year's dividend per share</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="6" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -1442,7 +1463,7 @@
           <t>Cost of equity (0-1)</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="12" t="n">
         <v>0.09</v>
       </c>
     </row>
@@ -1452,7 +1473,7 @@
           <t>Dividend growth (0-1)</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="12" t="n">
         <v>0.04</v>
       </c>
     </row>
@@ -1462,7 +1483,7 @@
           <t>Today's share price</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="6" t="n">
         <v>28</v>
       </c>
     </row>
@@ -1479,7 +1500,7 @@
           <t>Value per share</t>
         </is>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="8">
         <f>B5/(B6-B7)</f>
         <v/>
       </c>
@@ -1490,7 +1511,7 @@
           <t>Value at growth +1 point</t>
         </is>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="8">
         <f>B5/(B6-(B7+0.01))</f>
         <v/>
       </c>
@@ -1501,7 +1522,7 @@
           <t>Value at growth −1 point</t>
         </is>
       </c>
-      <c r="B13" s="5">
+      <c r="B13" s="8">
         <f>B5/(B6-(B7-0.01))</f>
         <v/>
       </c>
@@ -1512,7 +1533,7 @@
           <t>Value ÷ price</t>
         </is>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="11">
         <f>B11/B8</f>
         <v/>
       </c>
@@ -1524,6 +1545,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1531,7 +1553,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1568,7 +1590,7 @@
           <t>Bond yield to maturity (%)</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="17" t="n">
         <v>5.9</v>
       </c>
     </row>
@@ -1578,7 +1600,7 @@
           <t>Treasury yield, same maturity (%)</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="17" t="n">
         <v>4.2</v>
       </c>
     </row>
@@ -1588,7 +1610,7 @@
           <t>Average spread for this rating (%)</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="17" t="n">
         <v>1.3</v>
       </c>
     </row>
@@ -1605,7 +1627,7 @@
           <t>Spread (points)</t>
         </is>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="18">
         <f>B5-B6</f>
         <v/>
       </c>
@@ -1616,7 +1638,7 @@
           <t>Spread against rating peers (points)</t>
         </is>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="18">
         <f>B10-B7</f>
         <v/>
       </c>
@@ -1628,6 +1650,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1635,7 +1658,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1672,7 +1695,7 @@
           <t>Portfolio return (%)</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="17" t="n">
         <v>9</v>
       </c>
     </row>
@@ -1682,7 +1705,7 @@
           <t>Risk-free rate (%)</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="17" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1692,7 +1715,7 @@
           <t>Volatility (%)</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="17" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1702,7 +1725,7 @@
           <t>Benchmark return (%)</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="17" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1712,7 +1735,7 @@
           <t>Benchmark volatility (%)</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="17" t="n">
         <v>16</v>
       </c>
     </row>
@@ -1729,7 +1752,7 @@
           <t>Portfolio Sharpe</t>
         </is>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="11">
         <f>(B5-B6)/B7</f>
         <v/>
       </c>
@@ -1740,12 +1763,13 @@
           <t>Benchmark Sharpe</t>
         </is>
       </c>
-      <c r="B13" s="5">
+      <c r="B13" s="11">
         <f>(B8-B6)/B9</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/templates/finance-calculators.xlsx
+++ b/templates/finance-calculators.xlsx
@@ -1126,7 +1126,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Operating cash flow per year</t>
+          <t>Cash available for debt service (operating cash flow + interest paid)</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
@@ -1166,7 +1166,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Operating cash flow in a bad year</t>
+          <t>Cash available for debt service in a bad year</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
@@ -1302,11 +1302,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cash investors put in</t>
+          <t>Cash investors put in, including deal fees</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>150000000</v>
+        <v>160000000</v>
       </c>
     </row>
     <row r="10">
@@ -1332,7 +1332,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Debt still owed at exit</t>
+          <t>Net debt at exit</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
